--- a/rules/CORE-000580/negative/01/data/unit-test-coreid-CG0325-negative01.xlsx
+++ b/rules/CORE-000580/negative/01/data/unit-test-coreid-CG0325-negative01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000580\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE8EDC9-043B-4E7D-8D62-5263A02333BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CC690F-1163-4CE6-81B6-33FD6D1835C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
   <si>
     <t>Product</t>
   </si>
@@ -157,9 +157,6 @@
     <t>E006</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>E007</t>
   </si>
   <si>
@@ -167,6 +164,15 @@
   </si>
   <si>
     <t>[ABSENT]</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>E005</t>
+  </si>
+  <si>
+    <t>P3M</t>
   </si>
 </sst>
 </file>
@@ -638,7 +644,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -669,7 +675,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -689,7 +695,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -709,7 +715,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -718,7 +724,7 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -729,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -749,7 +755,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -769,7 +775,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -789,7 +795,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -809,7 +815,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -818,7 +824,7 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -829,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -849,7 +855,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -869,10 +875,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -889,16 +895,13 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,16 +912,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,10 +932,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -946,13 +949,16 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -963,16 +969,16 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -983,16 +989,13 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
-      </c>
-      <c r="F18" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1003,16 +1006,16 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1023,10 +1026,10 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -1040,107 +1043,16 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="F21" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26">
-        <v>12</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1152,6 +1064,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -1346,14 +1262,18 @@
       <c r="B10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="5"/>
+      <c r="C10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -1365,11 +1285,11 @@
       <c r="C11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>44</v>
-      </c>
+      <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
@@ -1379,13 +1299,13 @@
         <v>29</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="D12" s="7"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="7" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
